--- a/data/trans_orig/IP1009-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3411</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>449</t>
+          <t>446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100187</t>
+          <t>100847</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94134</t>
+          <t>93683</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196958</t>
+          <t>196702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201449</t>
+          <t>201452</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3467</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95826</t>
+          <t>95865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163908</t>
+          <t>162546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3967</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123322</t>
+          <t>123808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>227950</t>
+          <t>228117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1096</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>635216</t>
+          <t>635425</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679091</t>
+          <t>679076</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316916</t>
+          <t>1316544</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322363</t>
+          <t>1322315</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,91%</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -3823,7 +3823,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>89492</t>
+          <t>89578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185044</t>
+          <t>185609</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3364</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202325</t>
+          <t>202279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223500</t>
+          <t>224087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>428556</t>
+          <t>427713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5538,7 +5538,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>669507</t>
+          <t>668865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>710380</t>
+          <t>709986</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1382427</t>
+          <t>1382458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79002</t>
+          <t>80014</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>178876</t>
+          <t>179146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4416</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108319</t>
+          <t>107368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>214044</t>
+          <t>213571</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7106,7 +7106,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5074</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>218759</t>
+          <t>219213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>207866</t>
+          <t>207886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429357</t>
+          <t>429751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7757,7 +7757,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57346</t>
+          <t>58095</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64227</t>
+          <t>64243</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124031</t>
+          <t>124574</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8080,7 +8080,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>711</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6617</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>664989</t>
+          <t>664811</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>670744</t>
+          <t>670735</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>703120</t>
+          <t>703321</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>709018</t>
+          <t>709026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1371035</t>
+          <t>1371533</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1378981</t>
+          <t>1378837</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1009-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3505</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4017</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3862</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5196</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>96866</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>94142</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>103271</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>100847</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>100335</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,96%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>96866</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>93683</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>96,04%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>296</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196702</t>
+          <t>196659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201452</t>
+          <t>201448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>104352</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1183,42 +1183,42 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1296,52 +1296,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>85970</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>87389</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>85970</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,107 +1408,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3473</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3453</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4178</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>98637</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>95859</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>98637</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>95865</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162546</t>
+          <t>163271</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>99332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67392</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>99332</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202074</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>200733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202074</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>698</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2807</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>126591</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>123390</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>126591</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>123808</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>228117</t>
+          <t>228603</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>127289</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>104120</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>127289</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>72392</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74870</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>72392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5531</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3431</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3684</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5527</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1144</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6915</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2893,74 +2893,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>682531</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>679072</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>683927</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,7%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>951</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>637775</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>635425</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>635172</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>682531</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>679076</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1977</t>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1316544</t>
+          <t>1316633</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1322315</t>
+          <t>1322378</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>684603</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>953</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>638856</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1029</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>684603</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3470,47 +3470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89763</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>88439</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>89763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,107 +3700,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3151</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>3,4%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -3813,74 +3813,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>92092</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89578</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>89579</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>96,6%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>273</t>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>185609</t>
+          <t>185902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>96111</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92729</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>96111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4156,47 +4156,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>86890</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>84205</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>86890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4391,102 +4391,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3349</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3716</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2777</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4361</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4779</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -4499,74 +4499,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>226245</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>223781</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>204963</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>202279</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>201912</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,19%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>321</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>226245</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>224087</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>618</t>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427713</t>
+          <t>428131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>226864</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>298</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205628</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>226864</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4842,47 +4842,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>149169</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5185,47 +5185,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>74038</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53911</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>74038</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2930</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5216</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3515</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5124</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -5528,74 +5528,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>712882</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>710571</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>971</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>672778</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>668865</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>668822</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>712882</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>709986</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>1988</t>
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1382458</t>
+          <t>1381826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1386963</t>
+          <t>1386964</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>713501</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>973</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>674081</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>713501</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,107 +5992,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3076</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3789</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4212</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>753</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3741</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6105,74 +6105,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>82337</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>80014</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>79301</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,3%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>270</t>
@@ -6185,7 +6185,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179146</t>
+          <t>178675</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99797</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>83090</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>99797</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,107 +6335,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4845</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1397</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5378</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4941</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4889</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111349</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>107901</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111349</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107368</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213571</t>
+          <t>213519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -6543,7 +6543,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112746</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>105714</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>112746</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6791,47 +6791,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>75428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>75428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3494</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1227</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4364</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3907</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2968</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>454</t>
+          <t>455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -7134,74 +7134,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>210266</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>207360</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>222350</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>219213</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>219670</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,45%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>210266</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>207886</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,59%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>639</t>
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>429751</t>
+          <t>428346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>433977</t>
+          <t>433976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>210854</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>223577</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>210854</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7477,47 +7477,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143088</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>136194</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143088</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7712,102 +7712,102 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3964</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>5,84%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2992</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3582</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>4636</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4338</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -7820,74 +7820,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>67108</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>63861</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,16%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>60482</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>58095</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>58049</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>99,01%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>95,1%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>67108</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>64243</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,94%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>94,72%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>184</t>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124574</t>
+          <t>124276</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>61087</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8055,102 +8055,102 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6553</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
           <t>2585</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>6691</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6310</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,11%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>711</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>6416</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>2402</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>9706</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -8163,107 +8163,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>707035</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>703184</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>709024</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1009</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>668917</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>664811</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>670735</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>665192</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>670739</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>99,89%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>707035</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>703321</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>709026</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1375952</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1370642</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1378767</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>99,62%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1375952</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>1371533</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1378837</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>709737</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>671502</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1017</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>709737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
